--- a/reports/OYPB_브랜드별_시딩_비용_광고성과_HAN_260907.xlsx
+++ b/reports/OYPB_브랜드별_시딩_비용_광고성과_HAN_260907.xlsx
@@ -405,43 +405,43 @@
     <xf numFmtId="10" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="2">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="2">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -843,7 +843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:Q28"/>
+  <dimension ref="B2:R29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.2"/>
   <cols>
     <col width="8.796875" customWidth="1" style="3" min="1" max="1"/>
@@ -853,17 +853,18 @@
     <col width="13.69921875" customWidth="1" style="3" min="7" max="10"/>
     <col width="9" customWidth="1" style="3" min="11" max="12"/>
     <col width="14" customWidth="1" style="35" min="12" max="12"/>
-    <col width="9" customWidth="1" style="3" min="13" max="13"/>
-    <col width="14" customWidth="1" style="3" min="14" max="14"/>
-    <col width="15" customWidth="1" style="3" min="15" max="16384"/>
-    <col width="9" customWidth="1" style="35" min="16" max="16"/>
-    <col width="38" customWidth="1" style="35" min="17" max="17"/>
+    <col width="8" customWidth="1" style="3" min="13" max="13"/>
+    <col width="9" customWidth="1" style="3" min="14" max="14"/>
+    <col width="14" customWidth="1" style="3" min="15" max="16384"/>
+    <col width="15" customWidth="1" style="35" min="16" max="16"/>
+    <col width="9" customWidth="1" style="35" min="17" max="17"/>
+    <col width="40" customWidth="1" style="35" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="2" ht="13.8" customHeight="1" s="35">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>OYPB 브랜드별 시딩 · 원고료 · 성과  (팩트 집계)</t>
+          <t>OYPB 브랜드별 시딩 · 비용 · 성과  (팩트 집계)</t>
         </is>
       </c>
       <c r="C2" s="2" t="n"/>
@@ -940,7 +941,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>UGC 수량</t>
+          <t>시딩 수량</t>
         </is>
       </c>
       <c r="D6" s="36" t="n"/>
@@ -957,18 +958,19 @@
       <c r="K6" s="37" t="n"/>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>원고료</t>
-        </is>
-      </c>
-      <c r="M6" s="37" t="n"/>
-      <c r="N6" s="5" t="inlineStr">
+          <t>시딩 비용</t>
+        </is>
+      </c>
+      <c r="M6" s="36" t="n"/>
+      <c r="N6" s="37" t="n"/>
+      <c r="O6" s="5" t="inlineStr">
         <is>
           <t>퍼포먼스 광고</t>
         </is>
       </c>
-      <c r="O6" s="36" t="n"/>
-      <c r="P6" s="37" t="n"/>
-      <c r="Q6" s="5" t="inlineStr">
+      <c r="P6" s="36" t="n"/>
+      <c r="Q6" s="37" t="n"/>
+      <c r="R6" s="5" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
@@ -1023,30 +1025,35 @@
       </c>
       <c r="L7" s="10" t="inlineStr">
         <is>
-          <t>원고료</t>
+          <t>금액</t>
         </is>
       </c>
       <c r="M7" s="10" t="inlineStr">
         <is>
+          <t>기준</t>
+        </is>
+      </c>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
           <t>CPV</t>
         </is>
       </c>
-      <c r="N7" s="10" t="inlineStr">
+      <c r="O7" s="10" t="inlineStr">
         <is>
           <t>광고비</t>
         </is>
       </c>
-      <c r="O7" s="10" t="inlineStr">
+      <c r="P7" s="10" t="inlineStr">
         <is>
           <t>전환 매출</t>
         </is>
       </c>
-      <c r="P7" s="10" t="inlineStr">
+      <c r="Q7" s="10" t="inlineStr">
         <is>
           <t>ROAS</t>
         </is>
       </c>
-      <c r="Q7" s="38" t="n"/>
+      <c r="R7" s="38" t="n"/>
     </row>
     <row r="8" ht="39.6" customHeight="1" s="35">
       <c r="B8" s="13" t="inlineStr">
@@ -1084,24 +1091,29 @@
         <f>J8/G8</f>
         <v/>
       </c>
-      <c r="L8" s="39" t="n">
+      <c r="L8" s="41" t="n">
         <v>186700000</v>
       </c>
-      <c r="M8" s="15">
+      <c r="M8" s="15" t="inlineStr">
+        <is>
+          <t>원고료</t>
+        </is>
+      </c>
+      <c r="N8" s="42">
         <f>L8/G8</f>
         <v/>
       </c>
-      <c r="N8" s="16" t="n">
+      <c r="O8" s="43" t="n">
         <v>33768439</v>
       </c>
-      <c r="O8" s="41" t="n">
+      <c r="P8" s="43" t="n">
         <v>102736712</v>
       </c>
-      <c r="P8" s="41">
-        <f>O8/N8</f>
-        <v/>
-      </c>
-      <c r="Q8" s="42" t="inlineStr">
+      <c r="Q8" s="43">
+        <f>P8/O8</f>
+        <v/>
+      </c>
+      <c r="R8" s="43" t="inlineStr">
         <is>
           <t>25년 4Q UGC 협업 첫 시작을 바탕으로 
 250%대 ROAS는 300% 이상으로 올라 섬</t>
@@ -1144,24 +1156,29 @@
         <f>J9/G9</f>
         <v/>
       </c>
-      <c r="L9" s="39" t="n">
+      <c r="L9" s="41" t="n">
         <v>66300000</v>
       </c>
-      <c r="M9" s="15">
+      <c r="M9" s="15" t="inlineStr">
+        <is>
+          <t>원고료</t>
+        </is>
+      </c>
+      <c r="N9" s="42">
         <f>L9/G9</f>
         <v/>
       </c>
-      <c r="N9" s="16" t="n">
+      <c r="O9" s="43" t="n">
         <v>124304394</v>
       </c>
-      <c r="O9" s="41" t="n">
+      <c r="P9" s="43" t="n">
         <v>729266288</v>
       </c>
-      <c r="P9" s="41">
-        <f>O9/N9</f>
-        <v/>
-      </c>
-      <c r="Q9" s="42" t="inlineStr">
+      <c r="Q9" s="43">
+        <f>P9/O9</f>
+        <v/>
+      </c>
+      <c r="R9" s="43" t="inlineStr">
         <is>
           <t>전체 퍼포먼스 광고비 44% 집행 · 전환 매출 49% 창출
 UGC&amp;협력광고 중심 티트리 라인 스케일업 필요</t>
@@ -1204,24 +1221,29 @@
         <f>J10/G10</f>
         <v/>
       </c>
-      <c r="L10" s="39" t="n">
+      <c r="L10" s="41" t="n">
         <v>61550000</v>
       </c>
-      <c r="M10" s="15">
+      <c r="M10" s="15" t="inlineStr">
+        <is>
+          <t>원고료</t>
+        </is>
+      </c>
+      <c r="N10" s="42">
         <f>L10/G10</f>
         <v/>
       </c>
-      <c r="N10" s="16" t="n">
+      <c r="O10" s="43" t="n">
         <v>133848</v>
       </c>
-      <c r="O10" s="41" t="n">
+      <c r="P10" s="43" t="n">
         <v>348140</v>
       </c>
-      <c r="P10" s="41">
-        <f>O10/N10</f>
-        <v/>
-      </c>
-      <c r="Q10" s="42" t="inlineStr">
+      <c r="Q10" s="43">
+        <f>P10/O10</f>
+        <v/>
+      </c>
+      <c r="R10" s="43" t="inlineStr">
         <is>
           <t>PR키트 진행 등 참여율 1위(1.73%)
 광고는 281건 중 1건만 집행</t>
@@ -1264,24 +1286,29 @@
         <f>J11/G11</f>
         <v/>
       </c>
-      <c r="L11" s="39" t="n">
+      <c r="L11" s="41" t="n">
         <v>37900000</v>
       </c>
-      <c r="M11" s="15">
+      <c r="M11" s="15" t="inlineStr">
+        <is>
+          <t>원고료</t>
+        </is>
+      </c>
+      <c r="N11" s="42">
         <f>L11/G11</f>
         <v/>
       </c>
-      <c r="N11" s="16" t="n">
+      <c r="O11" s="43" t="n">
         <v>56333229</v>
       </c>
-      <c r="O11" s="41" t="n">
+      <c r="P11" s="43" t="n">
         <v>172219558</v>
       </c>
-      <c r="P11" s="41">
-        <f>O11/N11</f>
-        <v/>
-      </c>
-      <c r="Q11" s="42" t="inlineStr">
+      <c r="Q11" s="43">
+        <f>P11/O11</f>
+        <v/>
+      </c>
+      <c r="R11" s="43" t="inlineStr">
         <is>
           <t>퍼포먼스 광고 성과는 전량 국내에서 발생
 최대 조회수 764,503뷰</t>
@@ -1324,28 +1351,33 @@
         <f>J12/G12</f>
         <v/>
       </c>
-      <c r="L12" s="39" t="n">
+      <c r="L12" s="41" t="n">
         <v>2331000</v>
       </c>
-      <c r="M12" s="15">
+      <c r="M12" s="15" t="inlineStr">
+        <is>
+          <t>청구</t>
+        </is>
+      </c>
+      <c r="N12" s="42">
         <f>L12/G12</f>
         <v/>
       </c>
-      <c r="N12" s="16" t="n">
+      <c r="O12" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="O12" s="41" t="n">
+      <c r="P12" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="P12" s="41" t="inlineStr">
+      <c r="Q12" s="43" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q12" s="42" t="inlineStr">
+      <c r="R12" s="43" t="inlineStr">
         <is>
           <t>26.06 NAD 크림 나노 시딩 테스트
-원고료 건당 333,000(마크업 포함) · 조회수·참여 저조</t>
+비용 건당 333,000(마크업 포함) · 조회수·참여 저조</t>
         </is>
       </c>
     </row>
@@ -1385,31 +1417,33 @@
         <f>J13/G13</f>
         <v/>
       </c>
-      <c r="L13" s="39" t="inlineStr">
+      <c r="L13" s="41" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="M13" s="15" t="inlineStr">
+        <is>
+          <t>청구</t>
+        </is>
+      </c>
+      <c r="N13" s="42">
+        <f>L13/G13</f>
+        <v/>
+      </c>
+      <c r="O13" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="43" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M13" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N13" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" s="41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q13" s="42" t="inlineStr">
-        <is>
-          <t>틱톡 68건 · 청구 30,000,000(2025 시딩 정산 내)
-36건 성과 확보 · 최대 2,954,129뷰 = 전체 1위</t>
+      <c r="R13" s="43" t="inlineStr">
+        <is>
+          <t>틱톡 68건 · 비용 30,000,000(마크업 포함)
+2025 시딩 정산 59,830,000원 내 · 최대 2,954,129뷰 = 전체 1위</t>
         </is>
       </c>
     </row>
@@ -1449,24 +1483,29 @@
         <f>J14/G14</f>
         <v/>
       </c>
-      <c r="L14" s="39" t="n">
+      <c r="L14" s="41" t="n">
         <v>32490000</v>
       </c>
-      <c r="M14" s="43">
+      <c r="M14" s="44" t="inlineStr">
+        <is>
+          <t>원고료</t>
+        </is>
+      </c>
+      <c r="N14" s="42">
         <f>L14/G14</f>
         <v/>
       </c>
-      <c r="N14" s="16" t="n">
+      <c r="O14" s="43" t="n">
         <v>14985030</v>
       </c>
-      <c r="O14" s="41" t="n">
+      <c r="P14" s="43" t="n">
         <v>118255596</v>
       </c>
-      <c r="P14" s="41">
-        <f>O14/N14</f>
-        <v/>
-      </c>
-      <c r="Q14" s="42" t="inlineStr">
+      <c r="Q14" s="43">
+        <f>P14/O14</f>
+        <v/>
+      </c>
+      <c r="R14" s="43" t="inlineStr">
         <is>
           <t>빅&amp;스몰웨이브의 시작(25.05)
 마이크로 IMC 성과 가장 잘 워킹하는 브랜드</t>
@@ -1509,24 +1548,29 @@
         <f>J15/G15</f>
         <v/>
       </c>
-      <c r="L15" s="39" t="n">
+      <c r="L15" s="41" t="n">
         <v>40750000</v>
       </c>
-      <c r="M15" s="15">
+      <c r="M15" s="15" t="inlineStr">
+        <is>
+          <t>원고료</t>
+        </is>
+      </c>
+      <c r="N15" s="42">
         <f>L15/G15</f>
         <v/>
       </c>
-      <c r="N15" s="16" t="n">
+      <c r="O15" s="43" t="n">
         <v>16409851</v>
       </c>
-      <c r="O15" s="41" t="n">
+      <c r="P15" s="43" t="n">
         <v>113788050</v>
       </c>
-      <c r="P15" s="41">
-        <f>O15/N15</f>
-        <v/>
-      </c>
-      <c r="Q15" s="42" t="inlineStr">
+      <c r="Q15" s="43">
+        <f>P15/O15</f>
+        <v/>
+      </c>
+      <c r="R15" s="43" t="inlineStr">
         <is>
           <t>JP 60건 건당 415,000 (21건은 26.09 진행 · 미발행)
 26.04 행사·올영픽 미존재로 협업 수량 증대 여지</t>
@@ -1569,25 +1613,30 @@
         <f>J16/G16</f>
         <v/>
       </c>
-      <c r="L16" s="39" t="n">
+      <c r="L16" s="41" t="n">
         <v>22500000</v>
       </c>
-      <c r="M16" s="43">
+      <c r="M16" s="44" t="inlineStr">
+        <is>
+          <t>원고료</t>
+        </is>
+      </c>
+      <c r="N16" s="42">
         <f>L16/G16</f>
         <v/>
       </c>
-      <c r="N16" s="16" t="n">
+      <c r="O16" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="O16" s="41" t="n">
+      <c r="P16" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="P16" s="41" t="inlineStr">
+      <c r="Q16" s="43" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q16" s="42" t="inlineStr">
+      <c r="R16" s="43" t="inlineStr">
         <is>
           <t>퍼포먼스 광고 미집행
 (브랜드 fade out)</t>
@@ -1630,24 +1679,29 @@
         <f>J17/G17</f>
         <v/>
       </c>
-      <c r="L17" s="39" t="n">
+      <c r="L17" s="41" t="n">
         <v>31680000</v>
       </c>
-      <c r="M17" s="15">
+      <c r="M17" s="15" t="inlineStr">
+        <is>
+          <t>원고료</t>
+        </is>
+      </c>
+      <c r="N17" s="42">
         <f>L17/G17</f>
         <v/>
       </c>
-      <c r="N17" s="16" t="n">
+      <c r="O17" s="43" t="n">
         <v>23514230</v>
       </c>
-      <c r="O17" s="41" t="n">
+      <c r="P17" s="43" t="n">
         <v>134432958</v>
       </c>
-      <c r="P17" s="41">
-        <f>O17/N17</f>
-        <v/>
-      </c>
-      <c r="Q17" s="42" t="inlineStr">
+      <c r="Q17" s="43">
+        <f>P17/O17</f>
+        <v/>
+      </c>
+      <c r="R17" s="43" t="inlineStr">
         <is>
           <t>IMD 26.09.07로 103건 확정(v8 77건은 부분집합)
 JP 32건 건당 415,000 · ROAS 572%</t>
@@ -1690,25 +1744,30 @@
         <f>J18/G18</f>
         <v/>
       </c>
-      <c r="L18" s="39" t="n">
+      <c r="L18" s="41" t="n">
         <v>3700000</v>
       </c>
-      <c r="M18" s="43">
+      <c r="M18" s="44" t="inlineStr">
+        <is>
+          <t>원고료</t>
+        </is>
+      </c>
+      <c r="N18" s="42">
         <f>L18/G18</f>
         <v/>
       </c>
-      <c r="N18" s="16" t="n">
+      <c r="O18" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="O18" s="41" t="n">
+      <c r="P18" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="P18" s="41" t="inlineStr">
+      <c r="Q18" s="43" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q18" s="42" t="inlineStr">
+      <c r="R18" s="43" t="inlineStr">
         <is>
           <t>26.07 UGC 첫 협업 · 퍼포먼스 광고 미집행
 원고료 마이크로 5건×20만 + 나노 27건×10만</t>
@@ -1751,24 +1810,29 @@
         <f>J19/G19</f>
         <v/>
       </c>
-      <c r="L19" s="39" t="n">
+      <c r="L19" s="41" t="n">
         <v>6300000</v>
       </c>
-      <c r="M19" s="15">
+      <c r="M19" s="15" t="inlineStr">
+        <is>
+          <t>원고료</t>
+        </is>
+      </c>
+      <c r="N19" s="45">
         <f>L19/G19</f>
         <v/>
       </c>
-      <c r="N19" s="44" t="n">
+      <c r="O19" s="43" t="n">
         <v>14086284</v>
       </c>
-      <c r="O19" s="41" t="n">
+      <c r="P19" s="43" t="n">
         <v>121998372</v>
       </c>
-      <c r="P19" s="41">
-        <f>O19/N19</f>
-        <v/>
-      </c>
-      <c r="Q19" s="42" t="inlineStr">
+      <c r="Q19" s="43">
+        <f>P19/O19</f>
+        <v/>
+      </c>
+      <c r="R19" s="43" t="inlineStr">
         <is>
           <t>전체 브랜드 중 ROAS 1위(866%)
 최저 CPA 확보</t>
@@ -1781,55 +1845,60 @@
           <t>올더베러</t>
         </is>
       </c>
-      <c r="C20" s="45" t="n">
+      <c r="C20" s="46" t="n">
         <v>8</v>
       </c>
-      <c r="D20" s="45" t="n">
+      <c r="D20" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="E20" s="45">
+      <c r="E20" s="46">
         <f>SUM(C20:D20)</f>
         <v/>
       </c>
-      <c r="F20" s="45" t="n">
+      <c r="F20" s="46" t="n">
         <v>8</v>
       </c>
-      <c r="G20" s="45" t="n">
+      <c r="G20" s="46" t="n">
         <v>396952</v>
       </c>
-      <c r="H20" s="45" t="n">
+      <c r="H20" s="46" t="n">
         <v>3355</v>
       </c>
-      <c r="I20" s="45" t="n">
+      <c r="I20" s="46" t="n">
         <v>85</v>
       </c>
-      <c r="J20" s="45">
+      <c r="J20" s="46">
         <f>H20+I20</f>
         <v/>
       </c>
-      <c r="K20" s="46">
+      <c r="K20" s="47">
         <f>J20/G20</f>
         <v/>
       </c>
-      <c r="L20" s="45" t="n">
+      <c r="L20" s="13" t="n">
         <v>2000000</v>
       </c>
-      <c r="M20" s="47">
+      <c r="M20" s="48" t="inlineStr">
+        <is>
+          <t>원고료</t>
+        </is>
+      </c>
+      <c r="N20" s="42">
         <f>L20/G20</f>
         <v/>
       </c>
-      <c r="N20" s="16" t="n">
+      <c r="O20" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="O20" s="41" t="n">
+      <c r="P20" s="43" t="n">
         <v>0</v>
       </c>
-      <c r="P20" s="41" t="inlineStr">
+      <c r="Q20" s="43" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q20" s="42" t="inlineStr">
+      <c r="R20" s="43" t="inlineStr">
         <is>
           <t>퍼포먼스 광고 미집행</t>
         </is>
@@ -1841,63 +1910,68 @@
           <t>합계</t>
         </is>
       </c>
-      <c r="C21" s="48">
+      <c r="C21" s="49">
         <f>SUM(C8:C20)</f>
         <v/>
       </c>
-      <c r="D21" s="48">
+      <c r="D21" s="49">
         <f>SUM(D8:D20)</f>
         <v/>
       </c>
-      <c r="E21" s="48">
+      <c r="E21" s="49">
         <f>SUM(E8:E20)</f>
         <v/>
       </c>
-      <c r="F21" s="48">
+      <c r="F21" s="49">
         <f>SUM(F8:F20)</f>
         <v/>
       </c>
-      <c r="G21" s="48">
+      <c r="G21" s="49">
         <f>SUM(G8:G20)</f>
         <v/>
       </c>
-      <c r="H21" s="48">
+      <c r="H21" s="49">
         <f>SUM(H8:H20)</f>
         <v/>
       </c>
-      <c r="I21" s="48">
+      <c r="I21" s="49">
         <f>SUM(I8:I20)</f>
         <v/>
       </c>
-      <c r="J21" s="48">
+      <c r="J21" s="49">
         <f>SUM(J8:J20)</f>
         <v/>
       </c>
-      <c r="K21" s="49">
+      <c r="K21" s="50">
         <f>J21/G21</f>
         <v/>
       </c>
-      <c r="L21" s="48">
+      <c r="L21" s="31">
         <f>SUM(L8:L20)</f>
         <v/>
       </c>
-      <c r="M21" s="50">
+      <c r="M21" s="51" t="inlineStr">
+        <is>
+          <t>혼합</t>
+        </is>
+      </c>
+      <c r="N21" s="52">
         <f>L21/G21</f>
         <v/>
       </c>
-      <c r="N21" s="51">
-        <f>SUM(N8:N20)</f>
-        <v/>
-      </c>
-      <c r="O21" s="52">
+      <c r="O21" s="53">
         <f>SUM(O8:O20)</f>
         <v/>
       </c>
-      <c r="P21" s="52">
-        <f>O21/N21</f>
-        <v/>
-      </c>
-      <c r="Q21" s="53" t="inlineStr">
+      <c r="P21" s="53">
+        <f>SUM(P8:P20)</f>
+        <v/>
+      </c>
+      <c r="Q21" s="53">
+        <f>P21/O21</f>
+        <v/>
+      </c>
+      <c r="R21" s="53" t="inlineStr">
         <is>
           <t>수량 2,165 / 성과 집계 2,112</t>
         </is>
@@ -1920,28 +1994,28 @@
     <row r="24">
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>※ 원고료 = 국내는 IMD 행 단위 기재값, JP는 확정 단가(웨이크메이크·컬러그램 건당 415,000 / 바이오힐보 건당 333,000 마크업 포함), 케어플러스는 시딩현황 기재값. 바이오힐보 US는 데이터 없음.</t>
+          <t>※ 시딩 비용 기준 — [원고료] 마크업·VAT 제외. 국내는 IMD 행 단위 기재값, JP는 확정 단가 건당 415,000, 케어플러스는 시딩현황 3,700,000.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>※ CPV = 원고료 ÷ 조회수. 브랜드별 세금계산서 귀속은 발행 내역에 브랜드 미귀속액 70,431,189원이 있어 산출하지 않았다.</t>
+          <t>※ 시딩 비용 기준 — [청구] 마크업 포함. 바이오힐보 JP 7건 × 333,000 = 2,331,000 / 바이오힐보 US 틱톡 30,000,000 (2025 시딩 정산 59,830,000원 내).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>※ 전체 청구 기준 — 세금계산서 발행 900,344,264원 (26.02~08 확정 840,514,264 + 2025 시딩 정산 59,830,000) ÷ 조회수 57,682,849 = CPV 15.61원 / ÷ 참여 391,960 = CPE 2,297원 / ÷ 2,165건 = 건당 415,863원</t>
+          <t>※ 합계 524,201,000원 = 원고료 기준 491,870,000 + 청구 기준 32,331,000. 기준이 섞여 있어 소계 CPV 9.09원은 참고값이다.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>※ 2025 시딩은 전량 59,830,000원 내에서 운영 — 바이오힐보 US 틱톡 68건 30,000,000 + 국내 272건 29,830,000</t>
+          <t>※ 전체 청구 기준 — 세금계산서 발행 900,344,264원 (26.02~08 확정 840,514,264 + 2025 시딩 정산 59,830,000) ÷ 조회수 57,682,849 = CPV 15.61원 / ÷ 참여 391,960 = CPE 2,297원 / ÷ 2,165건 = 건당 415,863원</t>
         </is>
       </c>
     </row>
@@ -1952,14 +2026,21 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>※ 브랜드별 세금계산서 귀속은 발행 내역에 브랜드 미귀속액 70,431,189원이 있어 산출하지 않았다.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="L6:N6"/>
     <mergeCell ref="B6:B7"/>
-    <mergeCell ref="L6:M6"/>
+    <mergeCell ref="O6:Q6"/>
     <mergeCell ref="C6:F6"/>
-    <mergeCell ref="Q6:Q7"/>
+    <mergeCell ref="R6:R7"/>
     <mergeCell ref="G6:K6"/>
-    <mergeCell ref="N6:P6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
